--- a/VerveStacks_ZWE/vt_vervestacks_ZWE_v1.xlsx
+++ b/VerveStacks_ZWE/vt_vervestacks_ZWE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57A9B973-F41A-4E65-A84D-E6B9199A1933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A884D77-D1F2-40DB-A7E0-90B8A245A166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{72D04580-5E98-496E-A871-05AF9246FA97}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{831C9D31-E552-4453-BD24-739F43077C52}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -770,7 +770,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908286EC-F523-4CCC-9FDE-6D0D16597B73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2EACF4-3B3D-44C7-8415-7E6C855C3139}">
   <dimension ref="B9:T24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1628,7 +1628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49672176-2996-4449-82CE-27DE4D32BCC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5785AC79-7581-4F2C-8646-F350D3B32000}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZWE/vt_vervestacks_ZWE_v1.xlsx
+++ b/VerveStacks_ZWE/vt_vervestacks_ZWE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A884D77-D1F2-40DB-A7E0-90B8A245A166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEA40B70-D927-4042-BCC6-4D8E5FA58C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{831C9D31-E552-4453-BD24-739F43077C52}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" xr2:uid="{E99A2A3B-20D5-481F-AE25-D711BA34E9F6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -135,12 +135,18 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>ep_solar_pv_001</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
     <t>ep_solar_pv_002</t>
   </si>
   <si>
-    <t>solar</t>
-  </si>
-  <si>
     <t>elc_spv_002</t>
   </si>
   <si>
@@ -150,16 +156,10 @@
     <t>elc_spv_003</t>
   </si>
   <si>
-    <t>ep_solar_pv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
+    <t>ep_solar_pv_004</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
   </si>
   <si>
     <t>ep_solar_pv_013</t>
@@ -168,6 +168,12 @@
     <t>elc_spv_013</t>
   </si>
   <si>
+    <t>ep_solar_pv_014</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
     <t>ep_solar_pv_015</t>
   </si>
   <si>
@@ -184,12 +190,6 @@
   </si>
   <si>
     <t>elc_spv_017</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_018</t>
-  </si>
-  <si>
-    <t>elc_spv_018</t>
   </si>
   <si>
     <t>ep_solar_pv_019</t>
@@ -770,7 +770,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2EACF4-3B3D-44C7-8415-7E6C855C3139}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6CBBCAA-D8A7-476D-91B5-EF4746DA6D53}">
   <dimension ref="B9:T24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -849,7 +849,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>7.3872000000000021E-2</v>
+        <v>8.8646400000000028E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -905,19 +905,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>9.0288000000000021E-2</v>
+        <v>0.17606160000000004</v>
       </c>
       <c r="F12">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G12">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H12">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I12">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -961,19 +961,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>9.0288000000000021E-2</v>
+        <v>0.17606160000000004</v>
       </c>
       <c r="F13">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G13">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H13">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I13">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J13" t="s">
         <v>18</v>
@@ -1017,19 +1017,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>9.0288000000000021E-2</v>
+        <v>0.17606160000000004</v>
       </c>
       <c r="F14">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G14">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H14">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I14">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J14" t="s">
         <v>19</v>
@@ -1073,19 +1073,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>9.0288000000000021E-2</v>
+        <v>0.17606160000000004</v>
       </c>
       <c r="F15">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G15">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H15">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I15">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J15" t="s">
         <v>20</v>
@@ -1129,19 +1129,19 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>9.0288000000000021E-2</v>
+        <v>0.17606160000000004</v>
       </c>
       <c r="F16">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G16">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H16">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I16">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J16" t="s">
         <v>21</v>
@@ -1185,19 +1185,19 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>9.0288000000000021E-2</v>
+        <v>0.17606160000000004</v>
       </c>
       <c r="F17">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G17">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H17">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I17">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
@@ -1241,19 +1241,19 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.13122</v>
+        <v>0.19206719999999997</v>
       </c>
       <c r="F18">
-        <v>3144</v>
+        <v>2757</v>
       </c>
       <c r="G18">
-        <v>43.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H18">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="I18">
-        <v>0.59565000000000001</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J18" t="s">
         <v>23</v>
@@ -1297,19 +1297,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.13122</v>
+        <v>0.19206719999999997</v>
       </c>
       <c r="F19">
-        <v>3144</v>
+        <v>2757</v>
       </c>
       <c r="G19">
-        <v>43.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H19">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="I19">
-        <v>0.59565000000000001</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J19" t="s">
         <v>24</v>
@@ -1353,19 +1353,19 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>9.0288000000000021E-2</v>
+        <v>0.17606160000000004</v>
       </c>
       <c r="F20">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G20">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H20">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I20">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J20" t="s">
         <v>25</v>
@@ -1409,19 +1409,19 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>9.3024000000000037E-2</v>
+        <v>0.18139680000000002</v>
       </c>
       <c r="F21">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G21">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H21">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I21">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J21" t="s">
         <v>26</v>
@@ -1465,19 +1465,19 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>9.3024000000000037E-2</v>
+        <v>0.18139680000000002</v>
       </c>
       <c r="F22">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G22">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H22">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I22">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J22" t="s">
         <v>27</v>
@@ -1521,19 +1521,19 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999998</v>
       </c>
       <c r="F23">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G23">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H23">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I23">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J23" t="s">
         <v>28</v>
@@ -1577,19 +1577,19 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999998</v>
       </c>
       <c r="F24">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G24">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H24">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I24">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J24" t="s">
         <v>29</v>
@@ -1628,7 +1628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5785AC79-7581-4F2C-8646-F350D3B32000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5CAAA74-DD14-42C3-8D0D-86678E026278}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1713,7 +1713,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G11">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H11">
         <v>4016.25</v>
@@ -1766,7 +1766,7 @@
         <v>2.6000000000000009E-2</v>
       </c>
       <c r="G12">
-        <v>0.28800000000000003</v>
+        <v>0.34559999999999996</v>
       </c>
       <c r="H12">
         <v>4016.25</v>
@@ -1819,7 +1819,7 @@
         <v>0.03</v>
       </c>
       <c r="G13">
-        <v>0.24300000000000002</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="H13">
         <v>2295</v>
@@ -1872,7 +1872,7 @@
         <v>0.12</v>
       </c>
       <c r="G14">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H14">
         <v>1955</v>
@@ -1925,7 +1925,7 @@
         <v>0.12</v>
       </c>
       <c r="G15">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H15">
         <v>1955</v>
@@ -1978,7 +1978,7 @@
         <v>0.12</v>
       </c>
       <c r="G16">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H16">
         <v>1955</v>
@@ -2031,7 +2031,7 @@
         <v>0.12</v>
       </c>
       <c r="G17">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H17">
         <v>1955</v>
@@ -2084,7 +2084,7 @@
         <v>0.22</v>
       </c>
       <c r="G18">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H18">
         <v>1955</v>
@@ -2137,7 +2137,7 @@
         <v>0.22</v>
       </c>
       <c r="G19">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H19">
         <v>1955</v>
@@ -2190,7 +2190,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="G20">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H20">
         <v>1700</v>
@@ -2243,7 +2243,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="G21">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H21">
         <v>1700</v>
@@ -2296,7 +2296,7 @@
         <v>0.05</v>
       </c>
       <c r="G22">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H22">
         <v>2295</v>
@@ -2349,7 +2349,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="G23">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H23">
         <v>1955</v>
@@ -2402,7 +2402,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="G24">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H24">
         <v>1955</v>
@@ -2455,7 +2455,7 @@
         <v>0.6</v>
       </c>
       <c r="G25">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H25">
         <v>1700</v>
@@ -2508,7 +2508,7 @@
         <v>0.6</v>
       </c>
       <c r="G26">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H26">
         <v>1700</v>
@@ -2608,10 +2608,10 @@
         <v>34</v>
       </c>
       <c r="E28">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="F28">
-        <v>1.4E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L28">
-        <v>0.186</v>
+        <v>0.189</v>
       </c>
       <c r="N28" t="s">
         <v>66</v>
@@ -2664,10 +2664,10 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>2021</v>
+        <v>2028</v>
       </c>
       <c r="F29">
-        <v>1.1999999999999999E-3</v>
+        <v>0.03</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2682,10 +2682,10 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L29">
-        <v>0.186</v>
+        <v>0.192</v>
       </c>
       <c r="N29" t="s">
         <v>66</v>
@@ -2711,19 +2711,19 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E30">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F30">
-        <v>1.8E-3</v>
+        <v>0.06</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L30">
-        <v>0.186</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="N30" t="s">
         <v>66</v>
@@ -2767,19 +2767,19 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E31">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="F31">
-        <v>1.2E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2794,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L31">
-        <v>0.18400000000000002</v>
+        <v>0.186</v>
       </c>
       <c r="N31" t="s">
         <v>66</v>
@@ -2832,10 +2832,10 @@
         <v>38</v>
       </c>
       <c r="E32">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F32">
-        <v>5.0000000000000001E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2850,10 +2850,10 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L32">
-        <v>0.189</v>
+        <v>0.186</v>
       </c>
       <c r="N32" t="s">
         <v>66</v>
@@ -2888,10 +2888,10 @@
         <v>38</v>
       </c>
       <c r="E33">
-        <v>2028</v>
+        <v>2022</v>
       </c>
       <c r="F33">
-        <v>0.03</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2906,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L33">
-        <v>0.192</v>
+        <v>0.186</v>
       </c>
       <c r="N33" t="s">
         <v>66</v>
@@ -2944,10 +2944,10 @@
         <v>40</v>
       </c>
       <c r="E34">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="F34">
-        <v>1E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L34">
-        <v>0.19500000000000001</v>
+        <v>0.18400000000000002</v>
       </c>
       <c r="N34" t="s">
         <v>66</v>
@@ -2991,19 +2991,19 @@
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E35">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F35">
-        <v>2.8000000000000001E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -3018,10 +3018,10 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L35">
-        <v>0.19503571428571426</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="N35" t="s">
         <v>66</v>
@@ -3047,19 +3047,19 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E36">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="F36">
-        <v>8.5000000000000006E-3</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -3074,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L36">
-        <v>0.19599999999999998</v>
+        <v>0.19503571428571426</v>
       </c>
       <c r="N36" t="s">
         <v>66</v>
@@ -3103,19 +3103,19 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E37">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="F37">
-        <v>0.09</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -3130,10 +3130,10 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L37">
-        <v>0.19544444444444445</v>
+        <v>0.19599999999999998</v>
       </c>
       <c r="N37" t="s">
         <v>66</v>
@@ -3168,10 +3168,10 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="F38">
-        <v>2.5000000000000001E-3</v>
+        <v>0.09</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -3186,10 +3186,10 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L38">
-        <v>0.19600000000000001</v>
+        <v>0.19544444444444445</v>
       </c>
       <c r="N38" t="s">
         <v>66</v>
@@ -3227,7 +3227,7 @@
         <v>2015</v>
       </c>
       <c r="F39">
-        <v>1.1699999999999999E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3245,7 +3245,7 @@
         <v>40</v>
       </c>
       <c r="L39">
-        <v>0.189</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="N39" t="s">
         <v>66</v>
@@ -3271,19 +3271,19 @@
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E40">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="F40">
-        <v>5.0000000000000001E-3</v>
+        <v>1.1699999999999999E-2</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L40">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
@@ -3315,10 +3315,10 @@
         <v>46</v>
       </c>
       <c r="E41">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F41">
-        <v>3.5000000000000003E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -3333,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L41">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
@@ -3350,10 +3350,10 @@
         <v>48</v>
       </c>
       <c r="E42">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="F42">
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -3371,7 +3371,7 @@
         <v>30</v>
       </c>
       <c r="L42">
-        <v>0.19800000000000001</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
@@ -3525,10 +3525,10 @@
         <v>52</v>
       </c>
       <c r="E47">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="F47">
-        <v>0.06</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -3543,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L47">
-        <v>0.19700000000000001</v>
+        <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">

--- a/VerveStacks_ZWE/vt_vervestacks_ZWE_v1.xlsx
+++ b/VerveStacks_ZWE/vt_vervestacks_ZWE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZWE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEA40B70-D927-4042-BCC6-4D8E5FA58C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C688A7A6-C361-4FD5-A619-007E0FA3A0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" xr2:uid="{E99A2A3B-20D5-481F-AE25-D711BA34E9F6}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" xr2:uid="{FD19424B-5CDA-4264-9A71-8A4019A47568}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -770,7 +770,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6CBBCAA-D8A7-476D-91B5-EF4746DA6D53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A646F5FE-99A9-433E-B11D-111A799F63D4}">
   <dimension ref="B9:T24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1628,7 +1628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5CAAA74-DD14-42C3-8D0D-86678E026278}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B679B668-E3A1-4FBF-B5F7-03050FB4E4C3}">
   <dimension ref="B9:T50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
